--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 05.09.2026 08:31 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 06.09.2026 08:48 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 06.09.2026 08:48 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 07.09.2026 09:36 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 07.09.2026 09:36 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 08.09.2026 09:00 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 08.09.2026 09:00 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 09.09.2026 09:06 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 09.09.2026 09:06 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 10.09.2026 09:05 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 10.09.2026 09:05 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 11.09.2026 09:02 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 12.09.2026 08:46 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 13.09.2026 09:40 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 13.09.2026 09:40 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 14.09.2026 10:04 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 15.09.2026 09:33 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 16.09.2026 09:26 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 16.09.2026 09:26 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 17.09.2026 09:36 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 17.09.2026 09:36 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 18.09.2026 09:08 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 18.09.2026 09:08 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 19.09.2026 08:55 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 19.09.2026 08:55 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 20.09.2026 09:25 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 20.09.2026 09:25 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 21.09.2026 10:09 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 21.09.2026 10:09 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 22.09.2026 09:26 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 22.09.2026 09:26 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 23.09.2026 09:27 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 23.09.2026 09:27 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 24.09.2026 09:27 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 24.09.2026 09:27 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 25.09.2026 09:45 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 26.09.2026 09:29 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 27.09.2026 10:09 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 27.09.2026 10:09 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 28.09.2026 11:10 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 28.09.2026 11:10 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 29.09.2026 10:51 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 30.09.2026 10:40 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 01.10.2026 11:07 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>
@@ -4068,7 +4068,7 @@
       </c>
       <c r="M11" s="14" t="inlineStr">
         <is>
-          <t>Anbindung des zukünftigen Abstellbahnhofs Untertürkheim an den Bahnhof Stuttgart Bad Cannstatt</t>
+          <t>Anbindung des zukünftigen Abstellbahnhofs Untertürkheim an den Bahnhof Stuttgart-Bad Cannstatt</t>
         </is>
       </c>
       <c r="N11" s="14" t="inlineStr">
@@ -29135,7 +29135,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Überweisung</t>
+          <t>Änderung des Überweisungsbeschlusses</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 01.10.2026 11:07 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 02.10.2026 10:41 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 02.10.2026 10:41 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 03.10.2026 10:00 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 03.10.2026 10:00 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 04.10.2026 10:43 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 04.10.2026 10:43 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 05.10.2026 11:46 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 05.10.2026 11:46 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 06.10.2026 11:27 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 06.10.2026 11:27 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 07.10.2026 11:17 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 07.10.2026 11:17 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 08.10.2026 11:33 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 08.10.2026 11:33 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 09.10.2026 11:28 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 09.10.2026 11:28 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 10.10.2026 10:46 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 10.10.2026 10:46 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 11.10.2026 10:58 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 11.10.2026 10:58 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 12.10.2026 12:21 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 13.10.2026 12:04 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 14.10.2026 09:40 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>
@@ -3798,7 +3798,7 @@
     </row>
     <row r="8">
       <c r="A8" s="13" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="B8" s="14">
         <f>IF(A8="","",YEAR(A8))</f>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2869,7 +2869,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Kleine Anfrage</t>
+          <t>Antwort</t>
         </is>
       </c>
       <c r="O4">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Antwort</t>
+          <t>Kleine Anfrage</t>
         </is>
       </c>
       <c r="O5">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 14.10.2026 09:40 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 15.10.2026 09:18 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2869,7 +2869,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Antwort</t>
+          <t>Kleine Anfrage</t>
         </is>
       </c>
       <c r="O4">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Kleine Anfrage</t>
+          <t>Antwort</t>
         </is>
       </c>
       <c r="O5">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 15.10.2026 09:18 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 16.10.2026 09:12 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2869,7 +2869,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Kleine Anfrage</t>
+          <t>Antwort</t>
         </is>
       </c>
       <c r="O4">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Antwort</t>
+          <t>Kleine Anfrage</t>
         </is>
       </c>
       <c r="O5">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 16.10.2026 09:12 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 17.10.2026 08:44 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 17.10.2026 08:44 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 18.10.2026 09:00 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2869,7 +2869,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Antwort</t>
+          <t>Kleine Anfrage</t>
         </is>
       </c>
       <c r="O4">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Kleine Anfrage</t>
+          <t>Antwort</t>
         </is>
       </c>
       <c r="O5">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 18.10.2026 09:00 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 19.10.2026 10:10 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2869,7 +2869,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Kleine Anfrage</t>
+          <t>Antwort</t>
         </is>
       </c>
       <c r="O4">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Antwort</t>
+          <t>Kleine Anfrage</t>
         </is>
       </c>
       <c r="O5">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 19.10.2026 10:10 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 20.10.2026 09:34 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 20.10.2026 09:34 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 21.10.2026 09:30 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 21.10.2026 09:30 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 22.10.2026 09:34 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 22.10.2026 09:34 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 23.10.2026 09:29 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 23.10.2026 09:29 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 24.10.2026 09:02 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2869,7 +2869,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Antwort</t>
+          <t>Kleine Anfrage</t>
         </is>
       </c>
       <c r="O4">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Kleine Anfrage</t>
+          <t>Antwort</t>
         </is>
       </c>
       <c r="O5">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 24.10.2026 09:02 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 25.10.2026 09:18 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 25.10.2026 09:18 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 26.10.2026 10:24 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2869,7 +2869,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Kleine Anfrage</t>
+          <t>Antwort</t>
         </is>
       </c>
       <c r="O4">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Antwort</t>
+          <t>Kleine Anfrage</t>
         </is>
       </c>
       <c r="O5">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 26.10.2026 10:24 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 27.10.2026 09:59 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 27.10.2026 09:59 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 28.10.2026 10:45 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2869,7 +2869,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Antwort</t>
+          <t>Kleine Anfrage</t>
         </is>
       </c>
       <c r="O4">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Kleine Anfrage</t>
+          <t>Antwort</t>
         </is>
       </c>
       <c r="O5">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 28.10.2026 10:45 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 29.10.2026 11:02 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 29.10.2026 11:02 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 30.10.2026 10:59 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2869,7 +2869,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Kleine Anfrage</t>
+          <t>Antwort</t>
         </is>
       </c>
       <c r="O4">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Antwort</t>
+          <t>Kleine Anfrage</t>
         </is>
       </c>
       <c r="O5">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 30.10.2026 10:59 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 31.10.2026 10:32 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>
